--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N154_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N154_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>57.99717194419154</v>
+        <v>9.424540440931127</v>
       </c>
       <c r="D2" t="n">
-        <v>57.57208751204563</v>
+        <v>9.355464220707415</v>
       </c>
       <c r="E2" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F2" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.88490624123907</v>
+        <v>6.968797264201348</v>
       </c>
       <c r="D3" t="n">
-        <v>42.3931906302609</v>
+        <v>6.888893477417396</v>
       </c>
       <c r="E3" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F3" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.68334740877658</v>
+        <v>8.561043953926195</v>
       </c>
       <c r="D4" t="n">
-        <v>52.29006445927677</v>
+        <v>8.497135474632476</v>
       </c>
       <c r="E4" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F4" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.89033680091476</v>
+        <v>5.182179730148648</v>
       </c>
       <c r="D5" t="n">
-        <v>31.4303419115781</v>
+        <v>5.107430560631441</v>
       </c>
       <c r="E5" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F5" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.5092910747749</v>
+        <v>3.657759799650921</v>
       </c>
       <c r="D6" t="n">
-        <v>22.01997929622105</v>
+        <v>3.57824663563592</v>
       </c>
       <c r="E6" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F6" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.06797943694952</v>
+        <v>6.836046658504298</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80706286927659</v>
+        <v>6.793647716257445</v>
       </c>
       <c r="E7" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F7" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.52812934578665</v>
+        <v>6.91082101869033</v>
       </c>
       <c r="D8" t="n">
-        <v>42.35291697588461</v>
+        <v>6.882349008581249</v>
       </c>
       <c r="E8" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F8" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>52.21423757159106</v>
+        <v>8.484813605383547</v>
       </c>
       <c r="D9" t="n">
-        <v>52.20406186419883</v>
+        <v>8.483160052932309</v>
       </c>
       <c r="E9" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F9" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.1003744633568</v>
+        <v>9.116310850295481</v>
       </c>
       <c r="D10" t="n">
-        <v>56.18649233079087</v>
+        <v>9.130305003753517</v>
       </c>
       <c r="E10" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F10" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.33959401476109</v>
+        <v>2.005184027398677</v>
       </c>
       <c r="D11" t="n">
-        <v>12.52956879563784</v>
+        <v>2.036054929291149</v>
       </c>
       <c r="E11" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F11" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>59.81333571958046</v>
+        <v>9.719667054431826</v>
       </c>
       <c r="D12" t="n">
-        <v>59.98627084580009</v>
+        <v>9.747769012442514</v>
       </c>
       <c r="E12" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F12" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.66973179050407</v>
+        <v>7.258831415956912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.01054043561457</v>
+        <v>7.314212820787367</v>
       </c>
       <c r="E13" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F13" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>42.37185289801563</v>
+        <v>6.88542609592754</v>
       </c>
       <c r="D14" t="n">
-        <v>42.62315719848931</v>
+        <v>6.926263044754513</v>
       </c>
       <c r="E14" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F14" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>51.7379191542306</v>
+        <v>8.407411862562473</v>
       </c>
       <c r="D15" t="n">
-        <v>52.11841818141945</v>
+        <v>8.469242954480661</v>
       </c>
       <c r="E15" t="n">
-        <v>13.13396297906899</v>
+        <v>2.134268984098711</v>
       </c>
       <c r="F15" t="n">
-        <v>13.18169179608232</v>
+        <v>2.142024916863377</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
